--- a/ALL_results_combined.xlsx
+++ b/ALL_results_combined.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahapthorp/Dropbox (Personal)/UNE/Supervision/Honours_2026/Amanda Wiltshire Honours project/ReadingTheRoom_R_Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FB587EE4-B790-1D45-A81F-8BCCE182FD54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9235FD-B8A2-1A4F-B060-041AFA7A5306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="480" windowWidth="27300" windowHeight="16180" xr2:uid="{70243105-9E51-4641-8790-F9D8E734B6B7}"/>
+    <workbookView xWindow="3500" yWindow="10260" windowWidth="27300" windowHeight="16180" xr2:uid="{70243105-9E51-4641-8790-F9D8E734B6B7}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL_results_combined" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="513">
   <si>
     <t>participant</t>
   </si>
@@ -1031,21 +1031,6 @@
     <t>not really but reading this question makes me think there is an element of provoking me into thinking differently about my decision making or responses thats for sure</t>
   </si>
   <si>
-    <t>69125fab19177a1958393215</t>
-  </si>
-  <si>
-    <t>My perceptions of social understanding and behaviours in certain situations</t>
-  </si>
-  <si>
-    <t>Yes, during the scenario test</t>
-  </si>
-  <si>
-    <t>Was a bit surprised that I was only in the 50th percentile</t>
-  </si>
-  <si>
-    <t>Only with the 5-scenario question, I thought maybe the answer was lower than what I would have expectd</t>
-  </si>
-  <si>
     <t>691d38f81ac511c57d68f093</t>
   </si>
   <si>
@@ -1080,12 +1065,6 @@
   </si>
   <si>
     <t>Fair</t>
-  </si>
-  <si>
-    <t>social behaviour and interpretations</t>
-  </si>
-  <si>
-    <t>Very well</t>
   </si>
   <si>
     <t>69309f7da595fb656eebdeb1</t>
@@ -2455,7 +2434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B08589C1-E623-0644-B867-D0F7C7FA0F9B}">
-  <dimension ref="A1:AZ103"/>
+  <dimension ref="A1:AZ101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:52">
@@ -6401,7 +6380,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -6437,16 +6416,16 @@
         <v>1949</v>
       </c>
       <c r="N26" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="O26" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="P26" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="Q26" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="R26">
         <v>2</v>
@@ -12244,7 +12223,7 @@
     </row>
     <row r="63" spans="1:52">
       <c r="A63">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
         <v>332</v>
@@ -12256,31 +12235,31 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="2">
-        <v>7</v>
+        <v>-8</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I63">
         <v>4</v>
       </c>
       <c r="J63">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K63">
-        <v>0.49206349206349198</v>
+        <v>0.82539682539682502</v>
       </c>
       <c r="L63">
-        <v>2120.9841269841299</v>
+        <v>2641.9682539682499</v>
       </c>
       <c r="M63">
-        <v>2066</v>
+        <v>2417</v>
       </c>
       <c r="N63" t="s">
         <v>333</v>
@@ -12295,7 +12274,7 @@
         <v>336</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S63">
         <v>1</v>
@@ -12304,31 +12283,31 @@
         <v>3</v>
       </c>
       <c r="U63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD63">
         <v>2</v>
@@ -12337,72 +12316,72 @@
         <v>1</v>
       </c>
       <c r="AF63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG63">
         <v>5</v>
       </c>
       <c r="AH63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ63">
+        <v>6</v>
+      </c>
+      <c r="AK63">
+        <v>5</v>
+      </c>
+      <c r="AL63">
+        <v>4</v>
+      </c>
+      <c r="AM63">
+        <v>2</v>
+      </c>
+      <c r="AN63">
+        <v>1</v>
+      </c>
+      <c r="AO63">
+        <v>1</v>
+      </c>
+      <c r="AP63">
+        <v>5</v>
+      </c>
+      <c r="AQ63">
+        <v>3</v>
+      </c>
+      <c r="AR63">
+        <v>2</v>
+      </c>
+      <c r="AS63">
         <v>7</v>
       </c>
-      <c r="AK63">
-        <v>6</v>
-      </c>
-      <c r="AL63">
-        <v>5</v>
-      </c>
-      <c r="AM63">
-        <v>2</v>
-      </c>
-      <c r="AN63">
-        <v>5</v>
-      </c>
-      <c r="AO63">
-        <v>5</v>
-      </c>
-      <c r="AP63">
-        <v>5</v>
-      </c>
-      <c r="AQ63">
-        <v>5</v>
-      </c>
-      <c r="AR63">
-        <v>3</v>
-      </c>
-      <c r="AS63">
-        <v>6</v>
-      </c>
       <c r="AT63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU63">
         <v>2</v>
       </c>
       <c r="AV63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX63">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AY63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AZ63">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:52">
       <c r="A64">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B64" t="s">
         <v>337</v>
@@ -12416,29 +12395,29 @@
       <c r="E64">
         <v>1</v>
       </c>
-      <c r="F64" s="2">
-        <v>-8</v>
+      <c r="F64">
+        <v>19</v>
       </c>
       <c r="G64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J64">
         <v>1</v>
       </c>
       <c r="K64">
-        <v>0.82539682539682502</v>
+        <v>0.44444444444444398</v>
       </c>
       <c r="L64">
-        <v>2641.9682539682499</v>
+        <v>3584.3492063492099</v>
       </c>
       <c r="M64">
-        <v>2417</v>
+        <v>2666</v>
       </c>
       <c r="N64" t="s">
         <v>338</v>
@@ -12450,10 +12429,10 @@
         <v>340</v>
       </c>
       <c r="Q64" t="s">
-        <v>341</v>
+        <v>61</v>
       </c>
       <c r="R64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S64">
         <v>1</v>
@@ -12468,19 +12447,19 @@
         <v>2</v>
       </c>
       <c r="W64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X64">
         <v>3</v>
       </c>
       <c r="Y64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB64">
         <v>2</v>
@@ -12495,123 +12474,123 @@
         <v>1</v>
       </c>
       <c r="AF64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL64">
         <v>4</v>
       </c>
       <c r="AM64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ64">
         <v>3</v>
       </c>
       <c r="AR64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ64">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:52">
       <c r="A65">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s">
+        <v>341</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>62</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>2</v>
+      </c>
+      <c r="I65">
+        <v>4</v>
+      </c>
+      <c r="J65">
+        <v>3</v>
+      </c>
+      <c r="K65">
+        <v>0.49206349206349198</v>
+      </c>
+      <c r="L65">
+        <v>4073.3968253968301</v>
+      </c>
+      <c r="M65">
+        <v>3085</v>
+      </c>
+      <c r="N65" t="s">
         <v>342</v>
       </c>
-      <c r="C65">
-        <v>1</v>
-      </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-      <c r="E65">
-        <v>1</v>
-      </c>
-      <c r="F65">
-        <v>19</v>
-      </c>
-      <c r="G65">
-        <v>1</v>
-      </c>
-      <c r="H65">
-        <v>2</v>
-      </c>
-      <c r="I65">
-        <v>6</v>
-      </c>
-      <c r="J65">
-        <v>1</v>
-      </c>
-      <c r="K65">
-        <v>0.44444444444444398</v>
-      </c>
-      <c r="L65">
-        <v>3584.3492063492099</v>
-      </c>
-      <c r="M65">
-        <v>2666</v>
-      </c>
-      <c r="N65" t="s">
+      <c r="O65" t="s">
+        <v>108</v>
+      </c>
+      <c r="P65" t="s">
         <v>343</v>
-      </c>
-      <c r="O65" t="s">
-        <v>344</v>
-      </c>
-      <c r="P65" t="s">
-        <v>345</v>
       </c>
       <c r="Q65" t="s">
         <v>61</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S65">
         <v>1</v>
@@ -12623,94 +12602,94 @@
         <v>3</v>
       </c>
       <c r="V65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X65">
         <v>3</v>
       </c>
       <c r="Y65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z65">
         <v>3</v>
       </c>
       <c r="AA65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK65">
         <v>6</v>
       </c>
       <c r="AL65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AM65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AS65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX65">
         <v>6</v>
       </c>
       <c r="AY65">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AZ65">
         <v>6</v>
@@ -12718,56 +12697,56 @@
     </row>
     <row r="66" spans="1:52">
       <c r="A66">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B66" t="s">
+        <v>344</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <v>47</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>4</v>
+      </c>
+      <c r="J66">
+        <v>2</v>
+      </c>
+      <c r="K66">
+        <v>0.65079365079365104</v>
+      </c>
+      <c r="L66">
+        <v>3216.9841269841299</v>
+      </c>
+      <c r="M66">
+        <v>2418</v>
+      </c>
+      <c r="N66" t="s">
+        <v>345</v>
+      </c>
+      <c r="O66" t="s">
         <v>346</v>
       </c>
-      <c r="C66">
-        <v>1</v>
-      </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-      <c r="E66">
-        <v>1</v>
-      </c>
-      <c r="F66">
-        <v>62</v>
-      </c>
-      <c r="G66">
-        <v>1</v>
-      </c>
-      <c r="H66">
-        <v>2</v>
-      </c>
-      <c r="I66">
-        <v>4</v>
-      </c>
-      <c r="J66">
-        <v>3</v>
-      </c>
-      <c r="K66">
-        <v>0.49206349206349198</v>
-      </c>
-      <c r="L66">
-        <v>4073.3968253968301</v>
-      </c>
-      <c r="M66">
-        <v>3085</v>
-      </c>
-      <c r="N66" t="s">
+      <c r="P66" t="s">
         <v>347</v>
       </c>
-      <c r="O66" t="s">
-        <v>108</v>
-      </c>
-      <c r="P66" t="s">
+      <c r="Q66" t="s">
         <v>348</v>
       </c>
-      <c r="Q66" t="s">
-        <v>61</v>
-      </c>
       <c r="R66">
         <v>2</v>
       </c>
@@ -12775,13 +12754,13 @@
         <v>1</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W66">
         <v>2</v>
@@ -12790,19 +12769,19 @@
         <v>3</v>
       </c>
       <c r="Y66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB66">
         <v>0</v>
       </c>
       <c r="AC66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD66">
         <v>0</v>
@@ -12811,75 +12790,75 @@
         <v>0</v>
       </c>
       <c r="AF66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK66">
         <v>6</v>
       </c>
       <c r="AL66">
+        <v>4</v>
+      </c>
+      <c r="AM66">
+        <v>3</v>
+      </c>
+      <c r="AN66">
+        <v>5</v>
+      </c>
+      <c r="AO66">
+        <v>2</v>
+      </c>
+      <c r="AP66">
+        <v>6</v>
+      </c>
+      <c r="AQ66">
+        <v>3</v>
+      </c>
+      <c r="AR66">
+        <v>4</v>
+      </c>
+      <c r="AS66">
+        <v>3</v>
+      </c>
+      <c r="AT66">
+        <v>5</v>
+      </c>
+      <c r="AU66">
+        <v>5</v>
+      </c>
+      <c r="AV66">
+        <v>6</v>
+      </c>
+      <c r="AW66">
+        <v>3</v>
+      </c>
+      <c r="AX66">
+        <v>6</v>
+      </c>
+      <c r="AY66">
+        <v>6</v>
+      </c>
+      <c r="AZ66">
         <v>7</v>
-      </c>
-      <c r="AM66">
-        <v>3</v>
-      </c>
-      <c r="AN66">
-        <v>1</v>
-      </c>
-      <c r="AO66">
-        <v>1</v>
-      </c>
-      <c r="AP66">
-        <v>5</v>
-      </c>
-      <c r="AQ66">
-        <v>2</v>
-      </c>
-      <c r="AR66">
-        <v>1</v>
-      </c>
-      <c r="AS66">
-        <v>6</v>
-      </c>
-      <c r="AT66">
-        <v>4</v>
-      </c>
-      <c r="AU66">
-        <v>1</v>
-      </c>
-      <c r="AV66">
-        <v>1</v>
-      </c>
-      <c r="AW66">
-        <v>3</v>
-      </c>
-      <c r="AX66">
-        <v>6</v>
-      </c>
-      <c r="AY66">
-        <v>2</v>
-      </c>
-      <c r="AZ66">
-        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:52">
       <c r="A67">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -12888,43 +12867,43 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67">
         <v>2</v>
       </c>
       <c r="I67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K67">
-        <v>0.57142857142857095</v>
+        <v>0.634920634920635</v>
       </c>
       <c r="L67">
-        <v>3013.5873015872999</v>
+        <v>2602.2380952381</v>
       </c>
       <c r="M67">
-        <v>2534</v>
+        <v>2435</v>
       </c>
       <c r="N67" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O67" t="s">
-        <v>108</v>
+        <v>351</v>
       </c>
       <c r="P67" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q67" t="s">
-        <v>61</v>
+        <v>353</v>
       </c>
       <c r="R67">
         <v>1</v>
@@ -12936,61 +12915,61 @@
         <v>1</v>
       </c>
       <c r="U67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF67">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL67">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AM67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AN67">
         <v>2</v>
@@ -12999,13 +12978,13 @@
         <v>1</v>
       </c>
       <c r="AP67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ67">
         <v>2</v>
       </c>
       <c r="AR67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS67">
         <v>6</v>
@@ -13020,13 +12999,13 @@
         <v>1</v>
       </c>
       <c r="AW67">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AX67">
         <v>7</v>
       </c>
       <c r="AY67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AZ67">
         <v>7</v>
@@ -13034,10 +13013,10 @@
     </row>
     <row r="68" spans="1:52">
       <c r="A68">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -13046,70 +13025,70 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I68">
         <v>4</v>
       </c>
       <c r="J68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K68">
-        <v>0.65079365079365104</v>
+        <v>0.61904761904761896</v>
       </c>
       <c r="L68">
-        <v>3216.9841269841299</v>
+        <v>4430.4285714285697</v>
       </c>
       <c r="M68">
-        <v>2418</v>
+        <v>3230</v>
       </c>
       <c r="N68" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="O68" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="P68" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q68" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="R68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S68">
         <v>1</v>
       </c>
       <c r="T68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U68">
         <v>2</v>
       </c>
       <c r="V68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W68">
         <v>2</v>
       </c>
       <c r="X68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA68">
         <v>1</v>
@@ -13130,43 +13109,43 @@
         <v>5</v>
       </c>
       <c r="AG68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH68">
         <v>5</v>
       </c>
       <c r="AI68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AJ68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AK68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN68">
         <v>5</v>
       </c>
       <c r="AO68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AR68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT68">
         <v>5</v>
@@ -13175,27 +13154,27 @@
         <v>5</v>
       </c>
       <c r="AV68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX68">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY68">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AZ68">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:52">
       <c r="A69">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -13207,43 +13186,43 @@
         <v>1</v>
       </c>
       <c r="F69">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I69">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J69">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K69">
-        <v>0.634920634920635</v>
+        <v>0.76190476190476197</v>
       </c>
       <c r="L69">
-        <v>2602.2380952381</v>
+        <v>2732.8888888888901</v>
       </c>
       <c r="M69">
-        <v>2435</v>
+        <v>2399</v>
       </c>
       <c r="N69" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="O69" t="s">
-        <v>358</v>
+        <v>202</v>
       </c>
       <c r="P69" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q69" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="R69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S69">
         <v>1</v>
@@ -13258,19 +13237,19 @@
         <v>1</v>
       </c>
       <c r="W69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X69">
         <v>1</v>
       </c>
       <c r="Y69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB69">
         <v>1</v>
@@ -13282,78 +13261,78 @@
         <v>1</v>
       </c>
       <c r="AE69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF69">
         <v>5</v>
       </c>
       <c r="AG69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH69">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AI69">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ69">
         <v>5</v>
       </c>
       <c r="AK69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL69">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AM69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN69">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AO69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ69">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AR69">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AS69">
         <v>6</v>
       </c>
       <c r="AT69">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AU69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW69">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AX69">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY69">
         <v>4</v>
       </c>
       <c r="AZ69">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:52">
       <c r="A70">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -13362,70 +13341,70 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J70">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K70">
-        <v>0.61904761904761896</v>
+        <v>0.76190476190476197</v>
       </c>
       <c r="L70">
-        <v>4430.4285714285697</v>
+        <v>2128.0634920634898</v>
       </c>
       <c r="M70">
-        <v>3230</v>
+        <v>2048</v>
       </c>
       <c r="N70" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O70" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P70" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q70" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="R70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S70">
         <v>1</v>
       </c>
       <c r="T70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA70">
         <v>1</v>
@@ -13434,84 +13413,84 @@
         <v>0</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD70">
         <v>0</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG70">
         <v>5</v>
       </c>
       <c r="AH70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AI70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ70">
         <v>3</v>
       </c>
       <c r="AK70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AL70">
         <v>5</v>
       </c>
       <c r="AM70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AO70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP70">
         <v>5</v>
       </c>
       <c r="AQ70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AR70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AS70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX70">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AZ70">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:52">
       <c r="A71">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -13520,43 +13499,43 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I71">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K71">
-        <v>0.76190476190476197</v>
+        <v>0.52380952380952395</v>
       </c>
       <c r="L71">
-        <v>2732.8888888888901</v>
+        <v>2625.6507936507901</v>
       </c>
       <c r="M71">
-        <v>2399</v>
+        <v>2366</v>
       </c>
       <c r="N71" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O71" t="s">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q71" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="R71">
         <v>3</v>
@@ -13565,111 +13544,111 @@
         <v>1</v>
       </c>
       <c r="T71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X71">
         <v>1</v>
       </c>
       <c r="Y71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB71">
         <v>1</v>
       </c>
       <c r="AC71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AH71">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AQ71">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AR71">
         <v>5</v>
       </c>
       <c r="AS71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW71">
         <v>6</v>
       </c>
       <c r="AX71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ71">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:52">
       <c r="A72">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -13678,10 +13657,10 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="G72">
         <v>2</v>
@@ -13690,31 +13669,31 @@
         <v>5</v>
       </c>
       <c r="I72">
-        <v>5</v>
-      </c>
-      <c r="J72">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="J72" t="s">
+        <v>52</v>
       </c>
       <c r="K72">
-        <v>0.76190476190476197</v>
+        <v>0.60317460317460303</v>
       </c>
       <c r="L72">
-        <v>2128.0634920634898</v>
+        <v>2774.6031746031699</v>
       </c>
       <c r="M72">
-        <v>2048</v>
+        <v>2550</v>
       </c>
       <c r="N72" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O72" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P72" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q72" t="s">
-        <v>374</v>
+        <v>61</v>
       </c>
       <c r="R72">
         <v>3</v>
@@ -13723,111 +13702,111 @@
         <v>1</v>
       </c>
       <c r="T72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U72">
         <v>3</v>
       </c>
       <c r="V72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X72">
         <v>3</v>
       </c>
       <c r="Y72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA72">
         <v>1</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF72">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH72">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AI72">
         <v>1</v>
       </c>
       <c r="AJ72">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AK72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL72">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM72">
         <v>3</v>
       </c>
       <c r="AN72">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ72">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AR72">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AS72">
         <v>3</v>
       </c>
       <c r="AT72">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AU72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW72">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX72">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AZ72">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:52">
       <c r="A73">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -13836,76 +13815,76 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="H73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J73">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K73">
-        <v>0.52380952380952395</v>
+        <v>0.80952380952380998</v>
       </c>
       <c r="L73">
-        <v>2625.6507936507901</v>
+        <v>2273.3968253968301</v>
       </c>
       <c r="M73">
-        <v>2366</v>
+        <v>2181</v>
       </c>
       <c r="N73" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O73" t="s">
-        <v>143</v>
+        <v>378</v>
       </c>
       <c r="P73" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q73" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="R73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S73">
         <v>1</v>
       </c>
       <c r="T73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U73">
         <v>3</v>
       </c>
       <c r="V73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y73">
         <v>2</v>
       </c>
       <c r="Z73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA73">
         <v>1</v>
       </c>
       <c r="AB73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC73">
         <v>3</v>
@@ -13917,75 +13896,75 @@
         <v>1</v>
       </c>
       <c r="AF73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AI73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ73">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN73">
         <v>5</v>
       </c>
       <c r="AO73">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ73">
         <v>4</v>
       </c>
       <c r="AR73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW73">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AX73">
         <v>4</v>
       </c>
       <c r="AY73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AZ73">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:52">
       <c r="A74">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -13997,7 +13976,7 @@
         <v>2</v>
       </c>
       <c r="F74">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="G74">
         <v>2</v>
@@ -14006,28 +13985,28 @@
         <v>5</v>
       </c>
       <c r="I74">
-        <v>6</v>
-      </c>
-      <c r="J74" t="s">
-        <v>52</v>
+        <v>12</v>
+      </c>
+      <c r="J74">
+        <v>6</v>
       </c>
       <c r="K74">
-        <v>0.60317460317460303</v>
+        <v>0.476190476190476</v>
       </c>
       <c r="L74">
-        <v>2774.6031746031699</v>
+        <v>5654.5555555555602</v>
       </c>
       <c r="M74">
-        <v>2550</v>
+        <v>3618</v>
       </c>
       <c r="N74" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O74" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P74" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q74" t="s">
         <v>61</v>
@@ -14039,13 +14018,13 @@
         <v>1</v>
       </c>
       <c r="T74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U74">
         <v>3</v>
       </c>
       <c r="V74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W74">
         <v>3</v>
@@ -14054,16 +14033,16 @@
         <v>3</v>
       </c>
       <c r="Y74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC74">
         <v>2</v>
@@ -14078,22 +14057,22 @@
         <v>5</v>
       </c>
       <c r="AG74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI74">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK74">
         <v>5</v>
       </c>
       <c r="AL74">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AM74">
         <v>3</v>
@@ -14102,48 +14081,48 @@
         <v>4</v>
       </c>
       <c r="AO74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP74">
         <v>6</v>
       </c>
       <c r="AQ74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT74">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AU74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ74">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:52">
       <c r="A75">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -14155,43 +14134,43 @@
         <v>1</v>
       </c>
       <c r="F75">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75">
         <v>2</v>
       </c>
       <c r="I75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K75">
-        <v>0.80952380952380998</v>
+        <v>0.55555555555555602</v>
       </c>
       <c r="L75">
-        <v>2273.3968253968301</v>
+        <v>3498.25396825397</v>
       </c>
       <c r="M75">
-        <v>2181</v>
+        <v>2923</v>
       </c>
       <c r="N75" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O75" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P75" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q75" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="R75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S75">
         <v>1</v>
@@ -14200,16 +14179,16 @@
         <v>1</v>
       </c>
       <c r="U75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V75">
         <v>2</v>
       </c>
       <c r="W75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y75">
         <v>2</v>
@@ -14224,31 +14203,31 @@
         <v>0</v>
       </c>
       <c r="AC75">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE75">
         <v>1</v>
       </c>
       <c r="AF75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG75">
         <v>5</v>
       </c>
       <c r="AH75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI75">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AJ75">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK75">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AL75">
         <v>4</v>
@@ -14257,10 +14236,10 @@
         <v>5</v>
       </c>
       <c r="AN75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO75">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AP75">
         <v>4</v>
@@ -14272,36 +14251,36 @@
         <v>4</v>
       </c>
       <c r="AS75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU75">
         <v>3</v>
       </c>
       <c r="AV75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW75">
         <v>3</v>
       </c>
       <c r="AX75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ75">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:52">
       <c r="A76">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -14310,156 +14289,156 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G76">
         <v>2</v>
       </c>
       <c r="H76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I76">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K76">
-        <v>0.476190476190476</v>
+        <v>0.55555555555555602</v>
       </c>
       <c r="L76">
-        <v>5654.5555555555602</v>
+        <v>4805.3015873015902</v>
       </c>
       <c r="M76">
-        <v>3618</v>
+        <v>2649</v>
       </c>
       <c r="N76" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O76" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P76" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q76" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="R76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S76">
         <v>1</v>
       </c>
       <c r="T76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U76">
         <v>3</v>
       </c>
       <c r="V76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W76">
         <v>3</v>
       </c>
       <c r="X76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF76">
         <v>5</v>
       </c>
       <c r="AG76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ76">
         <v>5</v>
       </c>
       <c r="AK76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AN76">
         <v>4</v>
       </c>
       <c r="AO76">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AP76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AQ76">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AR76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AS76">
         <v>5</v>
       </c>
       <c r="AT76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AZ76">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:52">
       <c r="A77">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -14471,13 +14450,13 @@
         <v>1</v>
       </c>
       <c r="F77">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="G77">
         <v>2</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I77">
         <v>4</v>
@@ -14486,25 +14465,25 @@
         <v>3</v>
       </c>
       <c r="K77">
-        <v>0.55555555555555602</v>
+        <v>0.73015873015873001</v>
       </c>
       <c r="L77">
-        <v>3498.25396825397</v>
+        <v>2428.63492063492</v>
       </c>
       <c r="M77">
-        <v>2923</v>
+        <v>2133</v>
       </c>
       <c r="N77" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O77" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="P77" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q77" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="R77">
         <v>3</v>
@@ -14522,16 +14501,16 @@
         <v>2</v>
       </c>
       <c r="W77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA77">
         <v>1</v>
@@ -14540,10 +14519,10 @@
         <v>0</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE77">
         <v>1</v>
@@ -14558,66 +14537,66 @@
         <v>5</v>
       </c>
       <c r="AI77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL77">
         <v>4</v>
       </c>
       <c r="AM77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AR77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AS77">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AT77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV77">
         <v>3</v>
       </c>
       <c r="AW77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX77">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AZ77">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:52">
       <c r="A78">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -14629,49 +14608,49 @@
         <v>1</v>
       </c>
       <c r="F78">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G78">
         <v>2</v>
       </c>
       <c r="H78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I78">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K78">
-        <v>0.55555555555555602</v>
+        <v>0.57142857142857095</v>
       </c>
       <c r="L78">
-        <v>4805.3015873015902</v>
+        <v>3005.7619047619</v>
       </c>
       <c r="M78">
-        <v>2649</v>
+        <v>2418</v>
       </c>
       <c r="N78" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O78" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P78" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q78" t="s">
-        <v>110</v>
+        <v>402</v>
       </c>
       <c r="R78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S78">
         <v>1</v>
       </c>
       <c r="T78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U78">
         <v>3</v>
@@ -14680,102 +14659,102 @@
         <v>2</v>
       </c>
       <c r="W78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X78">
         <v>2</v>
       </c>
       <c r="Y78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z78">
         <v>3</v>
       </c>
       <c r="AA78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF78">
         <v>5</v>
       </c>
       <c r="AG78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AJ78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM78">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AN78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO78">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AP78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AQ78">
         <v>4</v>
       </c>
       <c r="AR78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AS78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT78">
         <v>4</v>
       </c>
       <c r="AU78">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ78">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:52">
       <c r="A79">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -14787,136 +14766,136 @@
         <v>1</v>
       </c>
       <c r="F79">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G79">
         <v>2</v>
       </c>
       <c r="H79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J79">
         <v>3</v>
       </c>
       <c r="K79">
-        <v>0.73015873015873001</v>
+        <v>0.46031746031746001</v>
       </c>
       <c r="L79">
-        <v>2428.63492063492</v>
+        <v>3682.1904761904798</v>
       </c>
       <c r="M79">
-        <v>2133</v>
+        <v>2934</v>
       </c>
       <c r="N79" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="O79" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="P79" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="Q79" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="R79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S79">
         <v>1</v>
       </c>
       <c r="T79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V79">
         <v>2</v>
       </c>
       <c r="W79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF79">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI79">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK79">
         <v>5</v>
       </c>
       <c r="AL79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO79">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ79">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AR79">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AS79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV79">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW79">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX79">
         <v>7</v>
@@ -14925,15 +14904,15 @@
         <v>6</v>
       </c>
       <c r="AZ79">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:52">
       <c r="A80">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -14948,7 +14927,7 @@
         <v>29</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80">
         <v>5</v>
@@ -14957,73 +14936,73 @@
         <v>4</v>
       </c>
       <c r="J80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K80">
-        <v>0.57142857142857095</v>
+        <v>0.66666666666666696</v>
       </c>
       <c r="L80">
-        <v>3005.7619047619</v>
+        <v>2016.2698412698401</v>
       </c>
       <c r="M80">
-        <v>2418</v>
+        <v>1983</v>
       </c>
       <c r="N80" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="O80" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="P80" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="Q80" t="s">
-        <v>409</v>
+        <v>61</v>
       </c>
       <c r="R80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S80">
         <v>1</v>
       </c>
       <c r="T80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U80">
         <v>3</v>
       </c>
       <c r="V80">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z80">
         <v>3</v>
       </c>
       <c r="AA80">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG80">
         <v>5</v>
@@ -15032,10 +15011,10 @@
         <v>5</v>
       </c>
       <c r="AI80">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK80">
         <v>5</v>
@@ -15044,37 +15023,37 @@
         <v>4</v>
       </c>
       <c r="AM80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN80">
         <v>3</v>
       </c>
       <c r="AO80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AQ80">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR80">
         <v>5</v>
       </c>
       <c r="AS80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT80">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU80">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW80">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX80">
         <v>6</v>
@@ -15088,10 +15067,10 @@
     </row>
     <row r="81" spans="1:52">
       <c r="A81">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -15103,136 +15082,136 @@
         <v>1</v>
       </c>
       <c r="F81">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G81">
         <v>2</v>
       </c>
       <c r="H81">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I81">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K81">
-        <v>0.46031746031746001</v>
+        <v>0.53968253968253999</v>
       </c>
       <c r="L81">
-        <v>3682.1904761904798</v>
+        <v>2533.6031746031699</v>
       </c>
       <c r="M81">
-        <v>2934</v>
+        <v>2433</v>
       </c>
       <c r="N81" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O81" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P81" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q81" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="R81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S81">
         <v>1</v>
       </c>
       <c r="T81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U81">
         <v>3</v>
       </c>
       <c r="V81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y81">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z81">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA81">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC81">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG81">
         <v>7</v>
       </c>
       <c r="AH81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI81">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AJ81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL81">
         <v>6</v>
       </c>
       <c r="AM81">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN81">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AO81">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AP81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ81">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AR81">
+        <v>2</v>
+      </c>
+      <c r="AS81">
         <v>7</v>
       </c>
-      <c r="AS81">
-        <v>5</v>
-      </c>
       <c r="AT81">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV81">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AW81">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX81">
         <v>7</v>
@@ -15241,15 +15220,15 @@
         <v>6</v>
       </c>
       <c r="AZ81">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:52">
       <c r="A82">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -15261,40 +15240,40 @@
         <v>1</v>
       </c>
       <c r="F82">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I82">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J82">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K82">
-        <v>0.66666666666666696</v>
+        <v>0.44444444444444398</v>
       </c>
       <c r="L82">
-        <v>2016.2698412698401</v>
+        <v>3114.7301587301599</v>
       </c>
       <c r="M82">
-        <v>1983</v>
+        <v>2683</v>
       </c>
       <c r="N82" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O82" t="s">
-        <v>417</v>
+        <v>202</v>
       </c>
       <c r="P82" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q82" t="s">
-        <v>61</v>
+        <v>420</v>
       </c>
       <c r="R82">
         <v>2</v>
@@ -15303,43 +15282,43 @@
         <v>1</v>
       </c>
       <c r="T82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y82">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z82">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB82">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD82">
         <v>1</v>
       </c>
       <c r="AE82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG82">
         <v>5</v>
@@ -15348,7 +15327,7 @@
         <v>5</v>
       </c>
       <c r="AI82">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AJ82">
         <v>5</v>
@@ -15357,7 +15336,7 @@
         <v>5</v>
       </c>
       <c r="AL82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM82">
         <v>5</v>
@@ -15366,31 +15345,31 @@
         <v>3</v>
       </c>
       <c r="AO82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS82">
         <v>5</v>
       </c>
       <c r="AT82">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AU82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV82">
         <v>4</v>
       </c>
       <c r="AW82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX82">
         <v>6</v>
@@ -15404,10 +15383,10 @@
     </row>
     <row r="83" spans="1:52">
       <c r="A83">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -15416,156 +15395,156 @@
         <v>0</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J83">
         <v>2</v>
       </c>
       <c r="K83">
-        <v>0.53968253968253999</v>
+        <v>0.44444444444444398</v>
       </c>
       <c r="L83">
-        <v>2533.6031746031699</v>
+        <v>19273.873015873</v>
       </c>
       <c r="M83">
-        <v>2433</v>
+        <v>17793</v>
       </c>
       <c r="N83" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O83" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P83" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Q83" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="R83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S83">
         <v>1</v>
       </c>
       <c r="T83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF83">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG83">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH83">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI83">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ83">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK83">
         <v>6</v>
       </c>
       <c r="AL83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM83">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN83">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AO83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP83">
         <v>6</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AR83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS83">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT83">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX83">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY83">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AZ83">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:52">
       <c r="A84">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -15577,43 +15556,43 @@
         <v>1</v>
       </c>
       <c r="F84">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H84">
         <v>4</v>
       </c>
       <c r="I84">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J84">
         <v>5</v>
       </c>
       <c r="K84">
-        <v>0.44444444444444398</v>
+        <v>0.74603174603174605</v>
       </c>
       <c r="L84">
-        <v>3114.7301587301599</v>
+        <v>2093.36507936508</v>
       </c>
       <c r="M84">
-        <v>2683</v>
+        <v>1972</v>
       </c>
       <c r="N84" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O84" t="s">
-        <v>202</v>
+        <v>428</v>
       </c>
       <c r="P84" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="Q84" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="R84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S84">
         <v>1</v>
@@ -15634,16 +15613,16 @@
         <v>2</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC84">
         <v>1</v>
@@ -15655,16 +15634,16 @@
         <v>1</v>
       </c>
       <c r="AF84">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG84">
         <v>5</v>
       </c>
       <c r="AH84">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI84">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ84">
         <v>5</v>
@@ -15673,34 +15652,34 @@
         <v>5</v>
       </c>
       <c r="AL84">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM84">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN84">
         <v>3</v>
       </c>
       <c r="AO84">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AP84">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ84">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR84">
         <v>4</v>
       </c>
       <c r="AS84">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT84">
         <v>4</v>
       </c>
       <c r="AU84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV84">
         <v>4</v>
@@ -15715,15 +15694,15 @@
         <v>5</v>
       </c>
       <c r="AZ84">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:52">
       <c r="A85">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -15732,43 +15711,43 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I85">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K85">
-        <v>0.44444444444444398</v>
+        <v>0.88888888888888895</v>
       </c>
       <c r="L85">
-        <v>19273.873015873</v>
+        <v>2400.5238095238101</v>
       </c>
       <c r="M85">
-        <v>17793</v>
+        <v>2177</v>
       </c>
       <c r="N85" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="O85" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="P85" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="Q85" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="R85">
         <v>2</v>
@@ -15780,108 +15759,108 @@
         <v>2</v>
       </c>
       <c r="U85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z85">
         <v>3</v>
       </c>
       <c r="AA85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF85">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AG85">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH85">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AJ85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AK85">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AL85">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AN85">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AO85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP85">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AQ85">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AR85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS85">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AT85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AU85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX85">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ85">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:52">
       <c r="A86">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -15893,40 +15872,40 @@
         <v>1</v>
       </c>
       <c r="F86">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H86">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I86">
         <v>4</v>
       </c>
       <c r="J86">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K86">
-        <v>0.74603174603174605</v>
+        <v>0.476190476190476</v>
       </c>
       <c r="L86">
-        <v>2093.36507936508</v>
+        <v>2556.2857142857101</v>
       </c>
       <c r="M86">
-        <v>1972</v>
+        <v>2232</v>
       </c>
       <c r="N86" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="O86" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="P86" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="Q86" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="R86">
         <v>3</v>
@@ -15935,7 +15914,7 @@
         <v>1</v>
       </c>
       <c r="T86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U86">
         <v>2</v>
@@ -15944,34 +15923,34 @@
         <v>2</v>
       </c>
       <c r="W86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG86">
         <v>5</v>
@@ -15980,16 +15959,16 @@
         <v>4</v>
       </c>
       <c r="AI86">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AJ86">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AK86">
         <v>5</v>
       </c>
       <c r="AL86">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM86">
         <v>3</v>
@@ -15998,37 +15977,37 @@
         <v>3</v>
       </c>
       <c r="AO86">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP86">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AQ86">
         <v>4</v>
       </c>
       <c r="AR86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS86">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU86">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW86">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX86">
         <v>6</v>
       </c>
       <c r="AY86">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AZ86">
         <v>5</v>
@@ -16036,10 +16015,10 @@
     </row>
     <row r="87" spans="1:52">
       <c r="A87">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -16051,7 +16030,7 @@
         <v>1</v>
       </c>
       <c r="F87">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G87">
         <v>2</v>
@@ -16063,31 +16042,31 @@
         <v>6</v>
       </c>
       <c r="J87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K87">
-        <v>0.88888888888888895</v>
+        <v>0.65079365079365104</v>
       </c>
       <c r="L87">
-        <v>2400.5238095238101</v>
+        <v>2065.50793650794</v>
       </c>
       <c r="M87">
-        <v>2177</v>
+        <v>1949</v>
       </c>
       <c r="N87" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="O87" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="P87" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="Q87" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="R87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S87">
         <v>1</v>
@@ -16096,61 +16075,61 @@
         <v>2</v>
       </c>
       <c r="U87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V87">
         <v>1</v>
       </c>
       <c r="W87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y87">
         <v>0</v>
       </c>
       <c r="Z87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE87">
         <v>0</v>
       </c>
       <c r="AF87">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG87">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH87">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI87">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ87">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AK87">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AL87">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM87">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN87">
         <v>1</v>
@@ -16159,34 +16138,34 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR87">
         <v>1</v>
       </c>
       <c r="AS87">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV87">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW87">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX87">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY87">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AZ87">
         <v>7</v>
@@ -16194,10 +16173,10 @@
     </row>
     <row r="88" spans="1:52">
       <c r="A88">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -16206,124 +16185,124 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>1</v>
-      </c>
-      <c r="F88">
-        <v>44</v>
+        <v>2</v>
+      </c>
+      <c r="F88" s="2">
+        <v>-9</v>
       </c>
       <c r="G88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I88">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J88">
         <v>1</v>
       </c>
       <c r="K88">
-        <v>0.476190476190476</v>
+        <v>0.50793650793650802</v>
       </c>
       <c r="L88">
-        <v>2556.2857142857101</v>
+        <v>3866.0476190476202</v>
       </c>
       <c r="M88">
-        <v>2232</v>
+        <v>2999</v>
       </c>
       <c r="N88" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="O88" t="s">
-        <v>445</v>
+        <v>202</v>
       </c>
       <c r="P88" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Q88" t="s">
-        <v>447</v>
+        <v>110</v>
       </c>
       <c r="R88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S88">
         <v>1</v>
       </c>
       <c r="T88">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U88">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V88">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X88">
         <v>3</v>
       </c>
       <c r="Y88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH88">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI88">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AJ88">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AK88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM88">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN88">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO88">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP88">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AQ88">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR88">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AS88">
         <v>5</v>
@@ -16332,30 +16311,30 @@
         <v>3</v>
       </c>
       <c r="AU88">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV88">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX88">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ88">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:52">
       <c r="A89">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -16364,70 +16343,70 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H89">
         <v>4</v>
       </c>
       <c r="I89">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J89">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K89">
-        <v>0.65079365079365104</v>
+        <v>0.74603174603174605</v>
       </c>
       <c r="L89">
-        <v>2065.50793650794</v>
+        <v>2308.1428571428601</v>
       </c>
       <c r="M89">
-        <v>1949</v>
+        <v>2100</v>
       </c>
       <c r="N89" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O89" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P89" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q89" t="s">
-        <v>452</v>
+        <v>61</v>
       </c>
       <c r="R89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S89">
         <v>1</v>
       </c>
       <c r="T89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA89">
         <v>0</v>
@@ -16439,22 +16418,22 @@
         <v>0</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE89">
         <v>0</v>
       </c>
       <c r="AF89">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG89">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH89">
         <v>3</v>
       </c>
       <c r="AI89">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AJ89">
         <v>6</v>
@@ -16463,25 +16442,25 @@
         <v>6</v>
       </c>
       <c r="AL89">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM89">
         <v>5</v>
       </c>
       <c r="AN89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AQ89">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AR89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS89">
         <v>6</v>
@@ -16490,7 +16469,7 @@
         <v>3</v>
       </c>
       <c r="AU89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV89">
         <v>4</v>
@@ -16499,18 +16478,18 @@
         <v>2</v>
       </c>
       <c r="AX89">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY89">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AZ89">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:52">
       <c r="A90">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B90" t="s">
         <v>453</v>
@@ -16522,58 +16501,58 @@
         <v>0</v>
       </c>
       <c r="E90">
-        <v>2</v>
-      </c>
-      <c r="F90" s="2">
-        <v>-9</v>
+        <v>1</v>
+      </c>
+      <c r="F90">
+        <v>46</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H90">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I90">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K90">
-        <v>0.50793650793650802</v>
+        <v>0.74603174603174605</v>
       </c>
       <c r="L90">
-        <v>3866.0476190476202</v>
+        <v>3399.5714285714298</v>
       </c>
       <c r="M90">
-        <v>2999</v>
+        <v>2180</v>
       </c>
       <c r="N90" t="s">
         <v>454</v>
       </c>
       <c r="O90" t="s">
-        <v>202</v>
+        <v>455</v>
       </c>
       <c r="P90" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q90" t="s">
-        <v>110</v>
+        <v>457</v>
       </c>
       <c r="R90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S90">
         <v>1</v>
       </c>
       <c r="T90">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U90">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W90">
         <v>3</v>
@@ -16582,96 +16561,96 @@
         <v>3</v>
       </c>
       <c r="Y90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC90">
         <v>3</v>
       </c>
       <c r="AD90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE90">
         <v>1</v>
       </c>
       <c r="AF90">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG90">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH90">
         <v>5</v>
       </c>
       <c r="AI90">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AJ90">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK90">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL90">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AM90">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN90">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO90">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AP90">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ90">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR90">
         <v>5</v>
       </c>
       <c r="AS90">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT90">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU90">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV90">
         <v>5</v>
       </c>
       <c r="AW90">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX90">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY90">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AZ90">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:52">
       <c r="A91">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -16683,43 +16662,43 @@
         <v>2</v>
       </c>
       <c r="F91">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="G91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91">
         <v>4</v>
       </c>
       <c r="I91">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J91">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K91">
         <v>0.74603174603174605</v>
       </c>
       <c r="L91">
-        <v>2308.1428571428601</v>
+        <v>2300.8888888888901</v>
       </c>
       <c r="M91">
-        <v>2100</v>
+        <v>2149</v>
       </c>
       <c r="N91" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O91" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="P91" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="Q91" t="s">
-        <v>61</v>
+        <v>462</v>
       </c>
       <c r="R91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S91">
         <v>1</v>
@@ -16728,16 +16707,16 @@
         <v>1</v>
       </c>
       <c r="U91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y91">
         <v>2</v>
@@ -16746,28 +16725,28 @@
         <v>2</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF91">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG91">
         <v>6</v>
       </c>
       <c r="AH91">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI91">
         <v>2</v>
@@ -16779,43 +16758,43 @@
         <v>6</v>
       </c>
       <c r="AL91">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM91">
         <v>5</v>
       </c>
       <c r="AN91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP91">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ91">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AR91">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AS91">
         <v>6</v>
       </c>
       <c r="AT91">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU91">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV91">
         <v>4</v>
       </c>
       <c r="AW91">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY91">
         <v>2</v>
@@ -16826,10 +16805,10 @@
     </row>
     <row r="92" spans="1:52">
       <c r="A92">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -16841,13 +16820,13 @@
         <v>1</v>
       </c>
       <c r="F92">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I92">
         <v>4</v>
@@ -16856,61 +16835,61 @@
         <v>2</v>
       </c>
       <c r="K92">
-        <v>0.74603174603174605</v>
+        <v>0.61904761904761896</v>
       </c>
       <c r="L92">
-        <v>3399.5714285714298</v>
+        <v>3982.6825396825402</v>
       </c>
       <c r="M92">
-        <v>2180</v>
+        <v>3334</v>
       </c>
       <c r="N92" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="O92" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="P92" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="Q92" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="R92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S92">
         <v>1</v>
       </c>
       <c r="T92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V92">
         <v>3</v>
       </c>
       <c r="W92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD92">
         <v>2</v>
@@ -16919,25 +16898,25 @@
         <v>1</v>
       </c>
       <c r="AF92">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG92">
         <v>5</v>
       </c>
       <c r="AH92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI92">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ92">
         <v>5</v>
       </c>
       <c r="AK92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL92">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM92">
         <v>4</v>
@@ -16946,48 +16925,48 @@
         <v>3</v>
       </c>
       <c r="AO92">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP92">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR92">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AS92">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT92">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU92">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV92">
         <v>5</v>
       </c>
       <c r="AW92">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX92">
         <v>6</v>
       </c>
       <c r="AY92">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ92">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:52">
       <c r="A93">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -16999,10 +16978,10 @@
         <v>2</v>
       </c>
       <c r="F93">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="G93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93">
         <v>4</v>
@@ -17011,28 +16990,28 @@
         <v>11</v>
       </c>
       <c r="J93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K93">
-        <v>0.74603174603174605</v>
+        <v>0.66666666666666696</v>
       </c>
       <c r="L93">
-        <v>2300.8888888888901</v>
+        <v>2214.61904761905</v>
       </c>
       <c r="M93">
-        <v>2149</v>
+        <v>2028</v>
       </c>
       <c r="N93" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="O93" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="P93" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="Q93" t="s">
-        <v>469</v>
+        <v>61</v>
       </c>
       <c r="R93">
         <v>3</v>
@@ -17041,46 +17020,46 @@
         <v>1</v>
       </c>
       <c r="T93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V93">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W93">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X93">
         <v>2</v>
       </c>
       <c r="Y93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z93">
         <v>2</v>
       </c>
       <c r="AA93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD93">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF93">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG93">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AH93">
         <v>4</v>
@@ -17092,13 +17071,13 @@
         <v>6</v>
       </c>
       <c r="AK93">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL93">
         <v>5</v>
       </c>
       <c r="AM93">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN93">
         <v>2</v>
@@ -17110,42 +17089,42 @@
         <v>5</v>
       </c>
       <c r="AQ93">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AR93">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AS93">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT93">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU93">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV93">
         <v>4</v>
       </c>
       <c r="AW93">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY93">
         <v>2</v>
       </c>
       <c r="AZ93">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:52">
       <c r="A94">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -17154,82 +17133,82 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="G94">
         <v>1</v>
       </c>
       <c r="H94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I94">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K94">
-        <v>0.61904761904761896</v>
+        <v>0.65079365079365104</v>
       </c>
       <c r="L94">
-        <v>3982.6825396825402</v>
+        <v>2767.9365079365102</v>
       </c>
       <c r="M94">
-        <v>3334</v>
+        <v>2421</v>
       </c>
       <c r="N94" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O94" t="s">
-        <v>472</v>
+        <v>202</v>
       </c>
       <c r="P94" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Q94" t="s">
-        <v>474</v>
+        <v>110</v>
       </c>
       <c r="R94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S94">
         <v>1</v>
       </c>
       <c r="T94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U94">
         <v>3</v>
       </c>
       <c r="V94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W94">
         <v>2</v>
       </c>
       <c r="X94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z94">
         <v>2</v>
       </c>
       <c r="AA94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB94">
         <v>2</v>
       </c>
       <c r="AC94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE94">
         <v>1</v>
@@ -17238,69 +17217,69 @@
         <v>5</v>
       </c>
       <c r="AG94">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK94">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP94">
         <v>5</v>
       </c>
       <c r="AQ94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR94">
         <v>3</v>
       </c>
       <c r="AS94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT94">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU94">
         <v>3</v>
       </c>
       <c r="AV94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW94">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX94">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY94">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AZ94">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:52">
       <c r="A95">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B95" t="s">
         <v>475</v>
@@ -17315,7 +17294,7 @@
         <v>2</v>
       </c>
       <c r="F95">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -17324,31 +17303,31 @@
         <v>4</v>
       </c>
       <c r="I95">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J95">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K95">
-        <v>0.66666666666666696</v>
+        <v>0.476190476190476</v>
       </c>
       <c r="L95">
-        <v>2214.61904761905</v>
+        <v>2638.7301587301599</v>
       </c>
       <c r="M95">
-        <v>2028</v>
+        <v>2465</v>
       </c>
       <c r="N95" t="s">
         <v>476</v>
       </c>
       <c r="O95" t="s">
+        <v>202</v>
+      </c>
+      <c r="P95" t="s">
         <v>477</v>
       </c>
-      <c r="P95" t="s">
-        <v>478</v>
-      </c>
       <c r="Q95" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="R95">
         <v>3</v>
@@ -17357,22 +17336,22 @@
         <v>1</v>
       </c>
       <c r="T95">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U95">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V95">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W95">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X95">
         <v>2</v>
       </c>
       <c r="Y95">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z95">
         <v>2</v>
@@ -17381,171 +17360,171 @@
         <v>0</v>
       </c>
       <c r="AB95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD95">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF95">
         <v>5</v>
       </c>
       <c r="AG95">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH95">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI95">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ95">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK95">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AL95">
         <v>5</v>
       </c>
       <c r="AM95">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN95">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO95">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AP95">
         <v>5</v>
       </c>
       <c r="AQ95">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR95">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AS95">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AT95">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU95">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV95">
         <v>4</v>
       </c>
       <c r="AW95">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY95">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AZ95">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96" spans="1:52">
       <c r="A96">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B96" t="s">
+        <v>478</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96">
+        <v>25</v>
+      </c>
+      <c r="G96">
+        <v>2</v>
+      </c>
+      <c r="H96">
+        <v>4</v>
+      </c>
+      <c r="I96">
+        <v>4</v>
+      </c>
+      <c r="J96">
+        <v>5</v>
+      </c>
+      <c r="K96">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="L96">
+        <v>2773.4603174603199</v>
+      </c>
+      <c r="M96">
+        <v>2350</v>
+      </c>
+      <c r="N96" t="s">
         <v>479</v>
       </c>
-      <c r="C96">
-        <v>1</v>
-      </c>
-      <c r="D96">
-        <v>0</v>
-      </c>
-      <c r="E96">
-        <v>2</v>
-      </c>
-      <c r="F96">
-        <v>21</v>
-      </c>
-      <c r="G96">
-        <v>1</v>
-      </c>
-      <c r="H96">
-        <v>3</v>
-      </c>
-      <c r="I96">
-        <v>6</v>
-      </c>
-      <c r="J96">
-        <v>1</v>
-      </c>
-      <c r="K96">
-        <v>0.65079365079365104</v>
-      </c>
-      <c r="L96">
-        <v>2767.9365079365102</v>
-      </c>
-      <c r="M96">
-        <v>2421</v>
-      </c>
-      <c r="N96" t="s">
+      <c r="O96" t="s">
         <v>480</v>
-      </c>
-      <c r="O96" t="s">
-        <v>202</v>
       </c>
       <c r="P96" t="s">
         <v>481</v>
       </c>
       <c r="Q96" t="s">
-        <v>110</v>
+        <v>482</v>
       </c>
       <c r="R96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S96">
         <v>1</v>
       </c>
       <c r="T96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U96">
         <v>3</v>
       </c>
       <c r="V96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W96">
         <v>2</v>
       </c>
       <c r="X96">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC96">
         <v>3</v>
       </c>
       <c r="AD96">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE96">
         <v>1</v>
@@ -17554,28 +17533,28 @@
         <v>5</v>
       </c>
       <c r="AG96">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH96">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ96">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK96">
         <v>6</v>
       </c>
       <c r="AL96">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM96">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO96">
         <v>2</v>
@@ -17584,42 +17563,42 @@
         <v>5</v>
       </c>
       <c r="AQ96">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR96">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AS96">
         <v>6</v>
       </c>
       <c r="AT96">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU96">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV96">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AW96">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX96">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY96">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AZ96">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:52">
       <c r="A97">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -17628,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -17640,31 +17619,31 @@
         <v>4</v>
       </c>
       <c r="I97">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J97">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K97">
-        <v>0.476190476190476</v>
+        <v>0.682539682539683</v>
       </c>
       <c r="L97">
-        <v>2638.7301587301599</v>
+        <v>2270.1111111111099</v>
       </c>
       <c r="M97">
-        <v>2465</v>
+        <v>2149</v>
       </c>
       <c r="N97" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O97" t="s">
-        <v>202</v>
+        <v>485</v>
       </c>
       <c r="P97" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="Q97" t="s">
-        <v>110</v>
+        <v>487</v>
       </c>
       <c r="R97">
         <v>3</v>
@@ -17673,22 +17652,22 @@
         <v>1</v>
       </c>
       <c r="T97">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y97">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z97">
         <v>2</v>
@@ -17697,19 +17676,19 @@
         <v>0</v>
       </c>
       <c r="AB97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD97">
         <v>1</v>
       </c>
       <c r="AE97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF97">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AG97">
         <v>5</v>
@@ -17718,7 +17697,7 @@
         <v>5</v>
       </c>
       <c r="AI97">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AJ97">
         <v>5</v>
@@ -17727,19 +17706,19 @@
         <v>5</v>
       </c>
       <c r="AL97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO97">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AP97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ97">
         <v>5</v>
@@ -17748,36 +17727,36 @@
         <v>5</v>
       </c>
       <c r="AS97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT97">
         <v>5</v>
       </c>
       <c r="AU97">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW97">
         <v>4</v>
       </c>
       <c r="AX97">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY97">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ97">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:52">
       <c r="A98">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -17789,7 +17768,7 @@
         <v>1</v>
       </c>
       <c r="F98">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="G98">
         <v>2</v>
@@ -17801,49 +17780,49 @@
         <v>4</v>
       </c>
       <c r="J98">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K98">
-        <v>0.71428571428571397</v>
+        <v>0.73015873015873001</v>
       </c>
       <c r="L98">
-        <v>2773.4603174603199</v>
+        <v>3486.1587301587301</v>
       </c>
       <c r="M98">
-        <v>2350</v>
+        <v>3035</v>
       </c>
       <c r="N98" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="O98" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="P98" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="Q98" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="R98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S98">
         <v>1</v>
       </c>
       <c r="T98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V98">
         <v>3</v>
       </c>
       <c r="W98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y98">
         <v>2</v>
@@ -17852,16 +17831,16 @@
         <v>3</v>
       </c>
       <c r="AA98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB98">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD98">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE98">
         <v>1</v>
@@ -17873,19 +17852,19 @@
         <v>6</v>
       </c>
       <c r="AH98">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ98">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK98">
         <v>6</v>
       </c>
       <c r="AL98">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM98">
         <v>4</v>
@@ -17897,34 +17876,31 @@
         <v>2</v>
       </c>
       <c r="AP98">
-        <v>5</v>
-      </c>
-      <c r="AQ98">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR98">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS98">
         <v>6</v>
       </c>
       <c r="AT98">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU98">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV98">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW98">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX98">
         <v>6</v>
       </c>
       <c r="AY98">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ98">
         <v>6</v>
@@ -17932,10 +17908,10 @@
     </row>
     <row r="99" spans="1:52">
       <c r="A99">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -17944,88 +17920,85 @@
         <v>0</v>
       </c>
       <c r="E99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="G99">
         <v>1</v>
       </c>
       <c r="H99">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I99">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J99">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K99">
-        <v>0.682539682539683</v>
+        <v>0.60317460317460303</v>
       </c>
       <c r="L99">
-        <v>2270.1111111111099</v>
+        <v>2201.49206349206</v>
       </c>
       <c r="M99">
-        <v>2149</v>
+        <v>2094</v>
       </c>
       <c r="N99" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="O99" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P99" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="Q99" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="R99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S99">
         <v>1</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V99">
-        <v>3</v>
-      </c>
-      <c r="W99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD99">
         <v>1</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF99">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG99">
         <v>5</v>
@@ -18034,7 +18007,7 @@
         <v>5</v>
       </c>
       <c r="AI99">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ99">
         <v>5</v>
@@ -18046,43 +18019,43 @@
         <v>4</v>
       </c>
       <c r="AM99">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN99">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO99">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AP99">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ99">
         <v>5</v>
       </c>
       <c r="AR99">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS99">
         <v>5</v>
       </c>
       <c r="AT99">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AU99">
         <v>1</v>
       </c>
       <c r="AV99">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW99">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX99">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY99">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AZ99">
         <v>6</v>
@@ -18090,10 +18063,10 @@
     </row>
     <row r="100" spans="1:52">
       <c r="A100">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -18102,76 +18075,73 @@
         <v>0</v>
       </c>
       <c r="E100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="G100">
         <v>2</v>
       </c>
       <c r="H100">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I100">
         <v>4</v>
       </c>
       <c r="J100">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K100">
-        <v>0.73015873015873001</v>
+        <v>0.71428571428571397</v>
       </c>
       <c r="L100">
-        <v>3486.1587301587301</v>
+        <v>2434.5238095238101</v>
       </c>
       <c r="M100">
-        <v>3035</v>
+        <v>2323</v>
       </c>
       <c r="N100" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="O100" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="P100" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="Q100" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="R100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S100">
         <v>1</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V100">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X100">
-        <v>2</v>
-      </c>
-      <c r="Y100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC100">
         <v>1</v>
@@ -18186,16 +18156,16 @@
         <v>5</v>
       </c>
       <c r="AG100">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH100">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ100">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK100">
         <v>6</v>
@@ -18204,19 +18174,22 @@
         <v>3</v>
       </c>
       <c r="AM100">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AN100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP100">
         <v>6</v>
       </c>
+      <c r="AQ100">
+        <v>6</v>
+      </c>
       <c r="AR100">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AS100">
         <v>6</v>
@@ -18225,30 +18198,30 @@
         <v>2</v>
       </c>
       <c r="AU100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV100">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AW100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX100">
         <v>6</v>
       </c>
       <c r="AY100">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ100">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:52">
       <c r="A101">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -18260,43 +18233,43 @@
         <v>2</v>
       </c>
       <c r="F101">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="G101">
         <v>1</v>
       </c>
       <c r="H101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I101">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K101">
-        <v>0.60317460317460303</v>
+        <v>0.58730158730158699</v>
       </c>
       <c r="L101">
-        <v>2201.49206349206</v>
+        <v>3168.3333333333298</v>
       </c>
       <c r="M101">
-        <v>2094</v>
+        <v>2926</v>
       </c>
       <c r="N101" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="O101" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="P101" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="Q101" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="R101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S101">
         <v>1</v>
@@ -18305,406 +18278,96 @@
         <v>2</v>
       </c>
       <c r="U101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V101">
+        <v>3</v>
+      </c>
+      <c r="W101">
         <v>2</v>
       </c>
       <c r="X101">
         <v>3</v>
       </c>
       <c r="Y101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z101">
-        <v>3</v>
-      </c>
-      <c r="AA101">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AB101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF101">
         <v>5</v>
       </c>
       <c r="AG101">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH101">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI101">
         <v>5</v>
       </c>
       <c r="AJ101">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK101">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL101">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM101">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN101">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AO101">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AP101">
         <v>5</v>
       </c>
       <c r="AQ101">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR101">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS101">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT101">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AU101">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV101">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW101">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX101">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY101">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ101">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" spans="1:52">
-      <c r="A102">
-        <v>101</v>
-      </c>
-      <c r="B102" t="s">
-        <v>505</v>
-      </c>
-      <c r="C102">
-        <v>1</v>
-      </c>
-      <c r="D102">
-        <v>0</v>
-      </c>
-      <c r="E102">
-        <v>2</v>
-      </c>
-      <c r="F102">
-        <v>49</v>
-      </c>
-      <c r="G102">
-        <v>2</v>
-      </c>
-      <c r="H102">
-        <v>3</v>
-      </c>
-      <c r="I102">
-        <v>4</v>
-      </c>
-      <c r="J102">
-        <v>4</v>
-      </c>
-      <c r="K102">
-        <v>0.71428571428571397</v>
-      </c>
-      <c r="L102">
-        <v>2434.5238095238101</v>
-      </c>
-      <c r="M102">
-        <v>2323</v>
-      </c>
-      <c r="N102" t="s">
-        <v>506</v>
-      </c>
-      <c r="O102" t="s">
-        <v>507</v>
-      </c>
-      <c r="P102" t="s">
-        <v>508</v>
-      </c>
-      <c r="Q102" t="s">
-        <v>509</v>
-      </c>
-      <c r="R102">
-        <v>3</v>
-      </c>
-      <c r="S102">
-        <v>1</v>
-      </c>
-      <c r="T102">
-        <v>1</v>
-      </c>
-      <c r="U102">
-        <v>3</v>
-      </c>
-      <c r="V102">
-        <v>4</v>
-      </c>
-      <c r="W102">
-        <v>3</v>
-      </c>
-      <c r="X102">
-        <v>1</v>
-      </c>
-      <c r="Z102">
-        <v>2</v>
-      </c>
-      <c r="AA102">
-        <v>2</v>
-      </c>
-      <c r="AB102">
-        <v>1</v>
-      </c>
-      <c r="AC102">
-        <v>1</v>
-      </c>
-      <c r="AD102">
-        <v>0</v>
-      </c>
-      <c r="AE102">
-        <v>1</v>
-      </c>
-      <c r="AF102">
-        <v>5</v>
-      </c>
-      <c r="AG102">
-        <v>7</v>
-      </c>
-      <c r="AH102">
-        <v>3</v>
-      </c>
-      <c r="AI102">
-        <v>1</v>
-      </c>
-      <c r="AJ102">
-        <v>5</v>
-      </c>
-      <c r="AK102">
-        <v>6</v>
-      </c>
-      <c r="AL102">
-        <v>3</v>
-      </c>
-      <c r="AM102">
-        <v>1</v>
-      </c>
-      <c r="AN102">
-        <v>2</v>
-      </c>
-      <c r="AO102">
-        <v>1</v>
-      </c>
-      <c r="AP102">
-        <v>6</v>
-      </c>
-      <c r="AQ102">
-        <v>6</v>
-      </c>
-      <c r="AR102">
-        <v>2</v>
-      </c>
-      <c r="AS102">
-        <v>6</v>
-      </c>
-      <c r="AT102">
-        <v>2</v>
-      </c>
-      <c r="AU102">
-        <v>1</v>
-      </c>
-      <c r="AV102">
-        <v>1</v>
-      </c>
-      <c r="AW102">
-        <v>2</v>
-      </c>
-      <c r="AX102">
-        <v>6</v>
-      </c>
-      <c r="AY102">
-        <v>5</v>
-      </c>
-      <c r="AZ102">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:52">
-      <c r="A103">
-        <v>102</v>
-      </c>
-      <c r="B103" t="s">
-        <v>510</v>
-      </c>
-      <c r="C103">
-        <v>1</v>
-      </c>
-      <c r="D103">
-        <v>0</v>
-      </c>
-      <c r="E103">
-        <v>2</v>
-      </c>
-      <c r="F103">
-        <v>61</v>
-      </c>
-      <c r="G103">
-        <v>1</v>
-      </c>
-      <c r="H103">
-        <v>3</v>
-      </c>
-      <c r="I103">
-        <v>4</v>
-      </c>
-      <c r="J103">
-        <v>2</v>
-      </c>
-      <c r="K103">
-        <v>0.58730158730158699</v>
-      </c>
-      <c r="L103">
-        <v>3168.3333333333298</v>
-      </c>
-      <c r="M103">
-        <v>2926</v>
-      </c>
-      <c r="N103" t="s">
-        <v>511</v>
-      </c>
-      <c r="O103" t="s">
-        <v>512</v>
-      </c>
-      <c r="P103" t="s">
-        <v>513</v>
-      </c>
-      <c r="Q103" t="s">
-        <v>514</v>
-      </c>
-      <c r="R103">
-        <v>3</v>
-      </c>
-      <c r="S103">
-        <v>1</v>
-      </c>
-      <c r="T103">
-        <v>2</v>
-      </c>
-      <c r="U103">
-        <v>3</v>
-      </c>
-      <c r="V103">
-        <v>3</v>
-      </c>
-      <c r="W103">
-        <v>2</v>
-      </c>
-      <c r="X103">
-        <v>3</v>
-      </c>
-      <c r="Y103">
-        <v>1</v>
-      </c>
-      <c r="Z103">
-        <v>2</v>
-      </c>
-      <c r="AB103">
-        <v>1</v>
-      </c>
-      <c r="AC103">
-        <v>2</v>
-      </c>
-      <c r="AD103">
-        <v>2</v>
-      </c>
-      <c r="AE103">
-        <v>2</v>
-      </c>
-      <c r="AF103">
-        <v>5</v>
-      </c>
-      <c r="AG103">
-        <v>4</v>
-      </c>
-      <c r="AH103">
-        <v>6</v>
-      </c>
-      <c r="AI103">
-        <v>5</v>
-      </c>
-      <c r="AJ103">
-        <v>6</v>
-      </c>
-      <c r="AK103">
-        <v>6</v>
-      </c>
-      <c r="AL103">
-        <v>6</v>
-      </c>
-      <c r="AM103">
-        <v>5</v>
-      </c>
-      <c r="AN103">
-        <v>6</v>
-      </c>
-      <c r="AO103">
-        <v>3</v>
-      </c>
-      <c r="AP103">
-        <v>5</v>
-      </c>
-      <c r="AQ103">
-        <v>4</v>
-      </c>
-      <c r="AR103">
-        <v>5</v>
-      </c>
-      <c r="AS103">
-        <v>6</v>
-      </c>
-      <c r="AT103">
-        <v>6</v>
-      </c>
-      <c r="AU103">
-        <v>4</v>
-      </c>
-      <c r="AV103">
-        <v>6</v>
-      </c>
-      <c r="AW103">
-        <v>5</v>
-      </c>
-      <c r="AX103">
-        <v>4</v>
-      </c>
-      <c r="AY103">
-        <v>5</v>
-      </c>
-      <c r="AZ103">
         <v>5</v>
       </c>
     </row>
